--- a/Topic Relevant Comments - Nigeria/Deyemi Okanlawon/Stop Raping Women Response.xlsx
+++ b/Topic Relevant Comments - Nigeria/Deyemi Okanlawon/Stop Raping Women Response.xlsx
@@ -55,15 +55,15 @@
     <t>"We need to stop child abuse. What about elder abuse? Domestic violence against women is a serious issue. What about male victims? Police brutality is out of control. What about crime rates?" Lool twitter is not a real place.</t>
   </si>
   <si>
+    <t>"Stop raping women" is a simple and clear message. I don't understand why there should be a counter. Saying talk about false accusations under every rape case is crazy. Ive not seen women bring up rape cases when false rape allegations is being discussed.</t>
+  </si>
+  <si>
     <t>there was a confirmed rape case that happened that week. Quickly explain how her statement isn't still valid</t>
   </si>
   <si>
     <t>Yes But Acknowledge RAPE IS BAD first Then Then talk about the false accusations... Replying straight with false accusations almost sound like you are against the "RAPE IS BAD" motion</t>
   </si>
   <si>
-    <t>"Stop raping women" is a simple and clear message. I don't understand why there should be a counter. Saying talk about false accusations under every rape case is crazy. Ive not seen women bring up rape cases when false rape allegations is being discussed.</t>
-  </si>
-  <si>
     <t>Both events are not mutually exclusive Mr. Deyemi. 1. Men, Do not rape a woman. 2. Women, do not falsely accuse men of rape. There is a possibility of occurrence and non-occurrence when a woman speaks up. From past patterns, it has become neccesary to adopt common sense.</t>
   </si>
   <si>
@@ -139,10 +139,13 @@
     <t>This is why I don't rate celebrities above what they are—humans. Stop rap!ng women, valid. Your dixk don rise. We never hear nor see you when young boys are speaking about how they were molested by older female adults. We never hear you when men are accused of r@pe falsely. With no due respect, stfu. Both conversations are important.</t>
   </si>
   <si>
+    <t>You won't force her to divert....she was standing on rape itself and wasn't done with that,and it is irrational to comment shut under that tweet...the percentage of false accusation is 2 and not a main topic at that time...y'all grow up</t>
+  </si>
+  <si>
     <t>Some of you really need to research before speaking. She said 'stop raping women.' Someone tried to shift it to false accusations, and she stayed on topic. That's not persecution that's focus. Bringing up false accusations in that moment does it even make sense? please answer???</t>
   </si>
   <si>
-    <t>You won't force her to divert....she was standing on rape itself and wasn't done with that,and it is irrational to comment shut under that tweet...the percentage of false accusation is 2 and not a main topic at that time...y'all grow up</t>
+    <t>There's no human on earth who had agreed to rape You all are just devil and you do look like who would accuse someone of false rape with that your forehead like ninja turtle That girl should be serving term now but she's not fuck you all miserable lot</t>
   </si>
   <si>
     <t>Lets stop acting blind and bias please. In as much as you're right, there's context and deep history in this particular subject. People on this app didn't just wake up overnight and start trying to speak up and ask questions about "False Rape Accusers". Is a crime that has been going on for yearssss now. People have died, men have unalived themselves, lost jobs, opportunities, contracts, families, friendships etc over false rape accusations. So whenever there's a rape case... People want to make sure it is true or false. So if you decide to speak about rape... You should equally speak about the other side of it. On our very eyes some group of women came together with bitterness and formed an evil coven called "feminist" ... every week on this app they were falsely accusing guys of abuse and rape. Nobody spoke up.. not a single celebrity spoke up.. And that's how the likes of Shola, Wiz, Neo etc came up and start speaking up regardless if you agree to some of their takes or not. Also... Simi has been doing this for years.. right since 2023. She's always trying to pretend like she's fighting for a good course ONLY when it involves a Woman. When is a Man on the victim side.. She goes silent. Everyone has clocked her. So let nobody try to be a moral police now. I have seen Men on this app drive away abusive and useless men. People like Kelvin Odanz can't come to this app again. Nobody is saying Simi shouldn't fight against Rape... actually, the penalty for rapist should be life in prison or hanging. But if you must fight for true course... COME CORRECT AND TRUE. That been said.... Why is the Mirabel girl and the other girl who also accused a poor boy that was arrested same week not yet in Police Custody? Now, imagine if the truth didn't come out and she actually pointed at a guy on her street. Imagine!?!?</t>
@@ -169,12 +172,12 @@
     <t>After the end of the day, that current trending r*pe case is a false accusations... What do you have to say about that?</t>
   </si>
   <si>
+    <t>It would have been a different thing if the rape on mirabel had been confirmed before she posted "stop raping women."</t>
+  </si>
+  <si>
     <t>Even if it comes from a rapist, yes it still remains and she didn't molest any child, no amount of crying will change that all bcos someone told you all not to rape, my God will continue to purnish all of you and I hope she makes one if you a scape goat, idiot</t>
   </si>
   <si>
-    <t>It would have been a different thing if the rape on mirabel had been confirmed before she posted "stop raping women."</t>
-  </si>
-  <si>
     <t>I beg to disagree sir. When you talk about rape case. You gats to talk about everything surrounding it. Including false accusations</t>
   </si>
   <si>
@@ -187,12 +190,12 @@
     <t>Thank you Deyemi School all them rape apologists!!</t>
   </si>
   <si>
+    <t>"Raping women" is indirectly calling all men rapist. Now tell us, how many men from your family has raped women before? Also how many women from your family has being raped before?</t>
+  </si>
+  <si>
     <t>"YES" is the only reasonable response to "stop raping women." Nobody is arguing against that. But let's not twist the situation, no one said men should rape women. That's a false framing of what actually happened. The issue was that she shut down people who were simply asking questions to make sure the accusation wasn't false. That's not defending rape that's asking for due process. And as we now know, the accusation turned out to be false, which proves why scrutiny matters. If you want to carry water for her, at least stick to the real context. Acting like anyone who asked for evidence was encouraging rape is manipulative and dishonest. Supporting victims does not require silencing questions or abandoning fairness.</t>
   </si>
   <si>
-    <t>"Raping women" is indirectly calling all men rapist. Now tell us, how many men from your family has raped women before? Also how many women from your family has being raped before?</t>
-  </si>
-  <si>
     <t>FALSE !!! If there are no clear evidences like Visuals or footage it is still allegedly. What if it was a False accusation what will then happen to the accused? Just forget about it and let go??? Note: I am never in support of a r@&amp;!St &amp; will never ever be.</t>
   </si>
   <si>
@@ -214,18 +217,18 @@
     <t>Whats famous is rarely wise. The conversation is not about rape. The rape issue was alleged to be false, confessed by the said victim. The issue on the ground is Simi exhibiting paedophilic traits. What is your comment on that?</t>
   </si>
   <si>
+    <t>All the men don't have to be rapist to agree to a good request/plea na</t>
+  </si>
+  <si>
     <t>One day the false accusations will reach your door step, you will look for people to defend you and all you will find is angry feminists.</t>
   </si>
   <si>
-    <t>All the men don't have to be rapist to agree to a good request/plea na</t>
+    <t>You are free to create a separate post about false accusations. What you cannot do is dictate that someone discussing rape must include your preferred topic. That does not make sense. If a statement condemning rape triggers you more than the crime itself, then you have a problem.</t>
   </si>
   <si>
     <t>I don't it cringe that some people reply a prostws to stop raping women with what about false rape allegations. Like WTF! We can pick the topics one at a time fgs!</t>
   </si>
   <si>
-    <t>You are free to create a separate post about false accusations. What you cannot do is dictate that someone discussing rape must include your preferred topic. That does not make sense. If a statement condemning rape triggers you more than the crime itself, then you have a problem.</t>
-  </si>
-  <si>
     <t>You're mixing things up. She was talking about rape as a general issue, not validating or dismissing any specific case. Let's not twist the context to fit a different argument Biko!!!</t>
   </si>
   <si>
@@ -334,12 +337,15 @@
     <t>You mock our brothers who are languishing in prison based on false rape accusations. I hope some day, you get 5 women falsely accusing you of raping them. Then you can come and post this shit after coming back from serving a 30-year stretch. You should have been in Thomas Partey's shoes without Thomas Partey's money to hire good lawyers. That's when we would be able to see how smart you really are.</t>
   </si>
   <si>
+    <t>We will be here when one of the Olosho actress will accuse you of rape that happened in 1998 just to destroy you, we go gather support her. We will do go-fund me just for you to enter prison. Continue running after pumeme.</t>
+  </si>
+  <si>
+    <t>A witch who accuses innocent men of false rape is talking about contradiction?</t>
+  </si>
+  <si>
     <t>Nobody disputed her that in short more than half of the people in her CS agreed with her, just few people asked "what about false rape accusers" then her response was STFU and una dey cry like say you don't know what really cause the issue Make una dey Mumu dey go</t>
   </si>
   <si>
-    <t>A witch who accuses innocent men of false rape is talking about contradiction?</t>
-  </si>
-  <si>
     <t>I get where you are going. But telling people to just say "yes" and never question anything feels off. Real justice needs truth and due process. Not pressure to stay silent. If people are afraid to ask questions, that's not accountability anymore.</t>
   </si>
   <si>
@@ -430,9 +436,6 @@
     <t>You have a point. But where she got it wrong was being vulgar when someone asked what about false r@pe accusations. She couldn't have just ignored the tweet rather than typing STFU. Meaning I don't F care about that. You know false r@pe accusations is a big deal.</t>
   </si>
   <si>
-    <t>Frankly speaking, Mr @_deyemi, Some of you should stick to your jobs and not reveal your foolishness after speaking. Imagine if it was you who made the statement about 4 year olds like Simi did. Pray you don't have issues, cos we'd remind you of this. x.com/i/status/2025946685411...</t>
-  </si>
-  <si>
     <t>When ur time come we go Dey here weak man na Una be enabler</t>
   </si>
   <si>
@@ -454,18 +457,21 @@
     <t>What is this one saying again? Can you read what you just tweeted? VERY WRONG oga deyem!</t>
   </si>
   <si>
-    <t>I been dey think say this guy get brain sha, this your tweet just define who exactly you are. Damn it</t>
-  </si>
-  <si>
     <t>You are totally wrong! Why did your friend that you came here to defend not just reply "yes" about false accusers but instead tried to silence someone who innocently asked her about false accusation? Can't you see you're just the same hypocrite and an unjust fellow?</t>
   </si>
   <si>
+    <t>Simple and short. I don't know what's going on with Nigerians. There are so many aspects to a conversation. Choose yours and let others choose theirs.</t>
+  </si>
+  <si>
     <t>Alaye! Respectfully,you too don't have sense. You know Mirabel case has almost successfully been sweep under the carpet but it's Simi receiving the bullets now. No go carry another person war for head óò!</t>
   </si>
   <si>
     <t>Hurts me so much when I see people I actually idolize turn out to be morons, I thought this guy was a smart guy until I came across this tweet. You could have just kept quiet mehn.</t>
   </si>
   <si>
+    <t>This man go make people go dig up him own past o</t>
+  </si>
+  <si>
     <t>Vee there is absolutely nothing to drag here, we just like dragging rubbish. the guy is absolutely right.</t>
   </si>
   <si>
@@ -511,6 +517,9 @@
     <t>So you are now conditioning people on how to talk about about r^pe and its associated cases because Simi is involved? When men who are supposed to make a decisive statement keep pandering and egging women's emotions, you just know he's performing for a crumbs of p#ssy</t>
   </si>
   <si>
+    <t>E no dey hard to detect feminine men END FALSE R^PE ACCUSATION</t>
+  </si>
+  <si>
     <t>Stop defending perverts. There is no law or rule that specify when to call out one crime over another. #HangTheRapists #HangThePedophile</t>
   </si>
   <si>
@@ -592,6 +601,9 @@
     <t>How about we talk about pedophiles</t>
   </si>
   <si>
+    <t>Big Love I so much love how you stand behind women. God bless you</t>
+  </si>
+  <si>
     <t>That stupid empathy would've transferred to David's case &amp; ultimately ruin him as we speak if someone had not interrupted the negative energy What's even wrong with all of you. So because she's a WOMAN means we can't say anything whenever she's wrong, abi kini gbogbo werey yi na</t>
   </si>
   <si>
@@ -604,19 +616,7 @@
     <t>I understand this defense but not to think of men when women say ## is unarguably and in this case it was FALSE still yet proven. U Dey find different conversation when it's all in same premises</t>
   </si>
   <si>
-    <t>Who be this one? If our reply must be YES? Then why are we replying? Or have you seen anyone say NO? Everyone in this life affirms this but moving on to a more recent trend in which birthed this whole back and forth cannot be overlooked so both situations are valid</t>
-  </si>
-  <si>
-    <t>Stupid men disgust me.</t>
-  </si>
-  <si>
-    <t>The idea of collective guilt is nauseating, an idea that we had to evolve from as a society. That is, in fact, the entire selling point of Christianity. The response should be yes. Why? Even by those who have never even seen the need to think of such evil in the first place? If you tell someone, "Stop singing," there is a baked-in presupposition that the person is singing. The same applies here, and the men who insist that they're not "singing" have every right to protest a statement that falsely presumes them to be singing. And if that protest involves bringing the dangers of "false singing accusations" into the conversation, so be it. There are far less toxic, less distracting, and more efficient ways of advocating against vices without resorting to low-resolution tactics that divide rather than unite everyone to address a vice.</t>
-  </si>
-  <si>
-    <t>Why does it always come up as a defense, instead of us treating each issue seriously and individually?</t>
-  </si>
-  <si>
-    <t>Exactly Mirabel lied If she was the victim ,we would have focused on her alone.</t>
+    <t>Why what's stopping you from talking about false accusers also</t>
   </si>
 </sst>
 </file>
